--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>26/07 18:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/07 19:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>27/07 17:15</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>65</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>45</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>21/07 18:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>50</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>27/07 18:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>45</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>27/07 17:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>26/07 23:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>25/07 16:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>45</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>26/07 21:30</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>60</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>45</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>24/07 18:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>45</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>40</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>26/07 15:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>40</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>21/07 09:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F20" t="n">
+        <v>2.7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>24.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>24</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>27/07 18:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>35</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>27/07 01:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>45</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F24" t="n">
+        <v>1.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>24/07 16:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
+      <c r="F25" t="n">
+        <v>1.27</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,187 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45859.0854080752</v>
+        <v>45859.0854080787</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CS 2 de Ma</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CS 2 de Mayo – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>25/07 21:30</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+19,2%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45859.17080232698</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Vitoria BA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vitoria BA – Sport RecifeSérie A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+10,9%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45859.17080232698</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Unirea </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FC Unirea 2004 Slobozia – FK Csikszereda Miercurea CiucLiga 1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21/07 16:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+6,29%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45859.17080232698</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Racing Club – Estudiantes de La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>27/07 00:15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+3,15%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45859.17080232698</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>25/07 21:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>50</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45859.17080232698</v>
+        <v>45859.17080232639</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>50</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45859.17080232698</v>
+        <v>45859.17080232639</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1623,8 @@
           <t>21/07 16:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>45</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1643,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45859.17080232698</v>
+        <v>45859.17080232639</v>
       </c>
     </row>
     <row r="29">
@@ -1672,10 +1666,8 @@
           <t>27/07 00:15</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>40</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1688,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45859.17080232698</v>
+        <v>45859.17080232639</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football | 1X | FC Vaduz –</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FC Vaduz – DungannonCoupes d'Europe - Europa Conference</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1X</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24/07 17:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>88,8%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+2,07%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45859.22898483029</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Tie-break: Oui | Giovanni M</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Giovanni Mpetshi Perricard – Aleksandar VukicATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Tie-break: Oui</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21/07 22:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>71,4%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+2,05%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45859.22898483029</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>24/07 17:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="F30" t="n">
+        <v>1.15</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45859.22898483029</v>
+        <v>45859.22898482639</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>21/07 22:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
+      <c r="F31" t="n">
+        <v>1.43</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,97 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45859.22898483029</v>
+        <v>45859.22898482639</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | San Martin</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>22/07 00:15</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+39,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45859.27489157684</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 21-2 | Zachary Sv</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Zachary Svajda – Miomir KecmanovicATP - Washington</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>80,7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+1,63%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45859.27489157684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45859.27489157684</v>
+        <v>45859.27489157407</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
+      <c r="F33" t="n">
+        <v>1.26</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45859.27489157684</v>
+        <v>45859.27489157407</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CA Banfield – Barracas CentralLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/07 23:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+5,95%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45859.31332838066</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Lincoln Re</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC – Etoile Rouge BelgradeLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22/07 16:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+1,63%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45859.31332838066</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>28/07 23:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>45</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45859.31332838066</v>
+        <v>45859.31332837963</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>22/07 16:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>45</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,277 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45859.31332838066</v>
+        <v>45859.31332837963</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | San Martin</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Martin de San Juan – Deportivo RiestraLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>22/07 00:15</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+49,0%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45859.3579914288</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | A.Potapova</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A.Potapova – V.MbokoWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>21/07 15:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+21,9%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45859.3579914288</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Gremio – A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gremio – Alianza LimaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>24/07 00:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+20,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45859.3579914288</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 2 - aces | L.Fernande</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>L.Fernandez – M.JointWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>21/07 16:10</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+18,2%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45859.3579914288</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | X - aces | M.Sakkari </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>M.Sakkari – K.BoulterWTA - Washington F</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>X - aces</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>21/07 22:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+8,26%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45859.3579914288</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | D.Lajovic </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D.Lajovic – T.AtmaneATP - Umag</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21/07 16:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+2,25%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45859.3579914288</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,10 +1967,8 @@
           <t>22/07 00:15</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>55</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
       </c>
     </row>
     <row r="37">
@@ -2012,10 +2010,8 @@
           <t>21/07 15:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>3</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
       </c>
     </row>
     <row r="38">
@@ -2057,10 +2053,8 @@
           <t>24/07 00:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>50</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2073,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
       </c>
     </row>
     <row r="39">
@@ -2102,10 +2096,8 @@
           <t>21/07 16:10</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F39" t="n">
+        <v>2.5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2118,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
       </c>
     </row>
     <row r="40">
@@ -2147,10 +2139,8 @@
           <t>21/07 22:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>7.75</t>
-        </is>
+      <c r="F40" t="n">
+        <v>7.75</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2163,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
       </c>
     </row>
     <row r="41">
@@ -2192,10 +2182,8 @@
           <t>21/07 16:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="F41" t="n">
+        <v>5.75</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2208,7 +2196,232 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45859.3579914288</v>
+        <v>45859.35799142361</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – Zrinjski MostarLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>22/07 18:15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+12,7%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45859.39703245711</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 2 - aces | B.Bonzi – </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B.Bonzi – F.MarozsanATP - Washington</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21/07 15:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45859.39703245711</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | FC Copenha</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>FC Copenhague – KF DritaLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>22/07 17:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+7,73%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45859.39703245711</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Beach volley | 21-2 | A.Besarab </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Beach volley</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>A.Besarab / P.Kantor – J.Van Langendonck / K.VercauterenFuture - Leuven</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21/07 10:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+4,84%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45859.39703245711</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Tennis | 11-2 | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Colton SmithWashington ATP</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>11-2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21/07 16:10</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>68,5%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+2,04%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45859.39703245711</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>22/07 18:15</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>50</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45859.39703245711</v>
+        <v>45859.3970324537</v>
       </c>
     </row>
     <row r="43">
@@ -2270,10 +2268,8 @@
           <t>21/07 15:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F43" t="n">
+        <v>2.5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2286,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45859.39703245711</v>
+        <v>45859.3970324537</v>
       </c>
     </row>
     <row r="44">
@@ -2315,10 +2311,8 @@
           <t>22/07 17:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2331,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45859.39703245711</v>
+        <v>45859.3970324537</v>
       </c>
     </row>
     <row r="45">
@@ -2360,10 +2354,8 @@
           <t>21/07 10:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
+      <c r="F45" t="n">
+        <v>1.55</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2376,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45859.39703245711</v>
+        <v>45859.3970324537</v>
       </c>
     </row>
     <row r="46">
@@ -2405,10 +2397,8 @@
           <t>21/07 16:10</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
+      <c r="F46" t="n">
+        <v>1.49</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2421,7 +2411,52 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45859.39703245711</v>
+        <v>45859.3970324537</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set1er participant | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Colton SmithATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21/07 16:10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+1,55%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45859.43541722918</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>21/07 16:10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F47" t="n">
+        <v>3.9</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,142 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45859.43541722918</v>
+        <v>45859.4354172338</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 1 - aces | Alvaro Gui</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Alvaro Guillen Meza – Stan WawrinkaATP - Umag</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>21/07 19:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>19,6%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+17,9%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45859.47281767513</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 5.51er set1er participant | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Colton SmithATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>21/07 16:10</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+7,01%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45859.47281767513</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set2e participant | Beibit Zhu</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Beibit Zhukayev – Alexandre MullerATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>21/07 16:10</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+1,99%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45859.47281767513</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2483,10 +2483,8 @@
           <t>21/07 19:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2499,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45859.47281767513</v>
+        <v>45859.47281767361</v>
       </c>
     </row>
     <row r="49">
@@ -2528,10 +2526,8 @@
           <t>21/07 16:10</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="F49" t="n">
+        <v>3.4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2544,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45859.47281767513</v>
+        <v>45859.47281767361</v>
       </c>
     </row>
     <row r="50">
@@ -2573,23 +2569,156 @@
           <t>21/07 16:10</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+1,99%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45859.47281767361</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Kamil Majc</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kamil Majchrzak – Pablo Llamas RuizATP - Umag</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>21/07 15:40</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+8,25%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45859.53513927369</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Sarmien</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CA Sarmiento – Atletico LanusLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>25/07 22:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+3,91%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45859.53513927369</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set1er participant | Gael Monfi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Gael Monfils – Yibing WuATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>4.40</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>+1,99%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>45859.47281767513</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+3,35%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45859.53513927369</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>21/07 15:40</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F51" t="n">
+        <v>2.75</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45859.53513927369</v>
+        <v>45859.53513927083</v>
       </c>
     </row>
     <row r="52">
@@ -2657,10 +2655,8 @@
           <t>25/07 22:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>50</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2673,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45859.53513927369</v>
+        <v>45859.53513927083</v>
       </c>
     </row>
     <row r="53">
@@ -2702,10 +2698,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
+      <c r="F53" t="n">
+        <v>4.4</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2718,7 +2712,142 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45859.53513927369</v>
+        <v>45859.53513927083</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 5.51er set1er participant | Gael Monfi</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Gael Monfils – Yibing WuATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+5,59%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45859.57004623442</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Benjamin B</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Benjamin Bonzi – Fabian MarozsanATP - Washington</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/07 15:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+5,12%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45859.57004623442</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Estudiante</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>21/07 22:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,90%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+4,65%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45859.57004623442</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F54" t="n">
+        <v>3.9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45859.57004623442</v>
+        <v>45859.57004623843</v>
       </c>
     </row>
     <row r="55">
@@ -2786,10 +2784,8 @@
           <t>21/07 15:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F55" t="n">
+        <v>2.35</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45859.57004623442</v>
+        <v>45859.57004623843</v>
       </c>
     </row>
     <row r="56">
@@ -2831,10 +2827,8 @@
           <t>21/07 22:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>55</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2847,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45859.57004623442</v>
+        <v>45859.57004623843</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Kauno Zalg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Kauno Zalgiris – Dainava AlytusLituanie. Lituanie - A Lyga</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21/07 16:30</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45859.60083238486</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Cerro Larg</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC – Central CordobaCopa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>22/07 22:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+7,74%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45859.60083238486</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>21/07 16:30</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>18</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45859.60083238486</v>
+        <v>45859.60083238426</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>22/07 22:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>45</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45859.60083238486</v>
+        <v>45859.60083238426</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ParionsSport(FR)Tennis | 1 - aces | A.Guillen </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A.Guillen Meza – S.WawrinkaATP - Umag</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21/07 19:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>7.25</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+42,5%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45859.64337560577</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Shkendi</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FK Shkendija – FCSBLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>22/07 18:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+6,81%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45859.64337560577</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>21/07 19:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>7.25</t>
-        </is>
+      <c r="F59" t="n">
+        <v>7.25</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45859.64337560577</v>
+        <v>45859.64337560185</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>22/07 18:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>50</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,97 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45859.64337560577</v>
+        <v>45859.64337560185</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball | H 2 (+13.5) | Italie (F)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Volleyball</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Italie (F) – États-Unis (F)International - Ligue des Nations (F)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>H 2 (+13.5)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/07 14:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+9,51%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45859.68760229534</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.51er set1er participant | Zachary Sv</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Zachary Svajda – Miomir KecmanovicATP 500 Washington</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 3.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>22/07 15:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+6,66%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45859.68760229534</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -3042,10 +3042,8 @@
           <t>23/07 14:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.55</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45859.68760229534</v>
+        <v>45859.68760229167</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>22/07 15:00</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3.1</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45859.68760229534</v>
+        <v>45859.68760229167</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3102,6 +3102,141 @@
         <v>45859.68760229167</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Slovan </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FC Slovan Liberec – FK PardubiceSynot League</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>27/07 13:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+20,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45859.7743990637</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Platens</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CA Platense – Argentinos JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>26/07 22:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+10,1%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45859.7743990637</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | FK Csiksze</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FK Csikszereda Miercurea Ciuc – Rapid BucarestLiga 1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>25/07 19:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45859.7743990637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>27/07 13:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>55</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45859.7743990637</v>
+        <v>45859.7743990625</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>26/07 22:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>50</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45859.7743990637</v>
+        <v>45859.7743990625</v>
       </c>
     </row>
     <row r="65">
@@ -3218,23 +3214,66 @@
           <t>25/07 19:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>45</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45859.7743990625</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Botosan</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FC Botosani – FC Unirea 2004 SloboziaLiga 1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>28/07 16:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>+10,0%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>45859.7743990637</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+8,49%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45859.80594469855</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-07-21.xlsx
+++ b/data/valuebets_database_2025-07-21.xlsx
@@ -3257,10 +3257,8 @@
           <t>28/07 16:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>45</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45859.80594469855</v>
+        <v>45859.80594469907</v>
       </c>
     </row>
   </sheetData>
